--- a/s2301_full.xlsx
+++ b/s2301_full.xlsx
@@ -609,7 +609,7 @@
     <col width="13" customWidth="1" min="142" max="142"/>
   </cols>
   <sheetData>
-    <row r="1" ht="60" customHeight="1">
+    <row r="1" ht="72" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Geography</t>
@@ -627,147 +627,147 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Total -- AGE -- 16 to 19 years</t>
+          <t>Total -- Population 16 years and over -- AGE -- 16 to 19 years</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Total -- AGE -- 20 to 24 years</t>
+          <t>Total -- Population 16 years and over -- AGE -- 20 to 24 years</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Total -- AGE -- 25 to 44 years</t>
+          <t>Total -- Population 16 years and over -- AGE -- 25 to 29 years</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Total -- AGE -- 45 to 54 years</t>
+          <t>Total -- Population 16 years and over -- AGE -- 30 to 34 years</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Total -- AGE -- 55 to 64 years</t>
+          <t>Total -- Population 16 years and over -- AGE -- 35 to 44 years</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Total -- AGE -- 65 to 74 years</t>
+          <t>Total -- Population 16 years and over -- AGE -- 45 to 54 years</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Total -- AGE -- 75 years and over</t>
+          <t>Total -- Population 16 years and over -- AGE -- 55 to 59 years</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Total -- RACE AND HISPANIC OR LATINO ORIGIN -- One race</t>
+          <t>Total -- Population 16 years and over -- AGE -- 60 to 64 years</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Total -- RACE AND HISPANIC OR LATINO ORIGIN -- One race -- White</t>
+          <t>Total -- Population 16 years and over -- AGE -- 65 to 74 years</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Total -- RACE AND HISPANIC OR LATINO ORIGIN -- One race -- Black or African American</t>
+          <t>Total -- Population 16 years and over -- AGE -- 75 years and over</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Total -- RACE AND HISPANIC OR LATINO ORIGIN -- One race -- American Indian and Alaska Native</t>
+          <t>Total -- Population 16 years and over -- RACE AND HISPANIC OR LATINO ORIGIN -- White alone</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Total -- RACE AND HISPANIC OR LATINO ORIGIN -- One race -- Asian</t>
+          <t>Total -- Population 16 years and over -- RACE AND HISPANIC OR LATINO ORIGIN -- Black or African American alone</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Total -- RACE AND HISPANIC OR LATINO ORIGIN -- One race -- Native Hawaiian and Other Pacific Islander</t>
+          <t>Total -- Population 16 years and over -- RACE AND HISPANIC OR LATINO ORIGIN -- American Indian and Alaska Native alone</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Total -- RACE AND HISPANIC OR LATINO ORIGIN -- One race -- Some other race</t>
+          <t>Total -- Population 16 years and over -- RACE AND HISPANIC OR LATINO ORIGIN -- Asian alone</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Total -- RACE AND HISPANIC OR LATINO ORIGIN -- Two or more races</t>
+          <t>Total -- Population 16 years and over -- RACE AND HISPANIC OR LATINO ORIGIN -- Native Hawaiian and Other Pacific Islander alone</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Total -- Hispanic or Latino origin (of any race)</t>
+          <t>Total -- Population 16 years and over -- RACE AND HISPANIC OR LATINO ORIGIN -- Some other race alone</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Total -- White alone, not Hispanic or Latino</t>
+          <t>Total -- Population 16 years and over -- RACE AND HISPANIC OR LATINO ORIGIN -- Two or more races</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Total -- Population 16 years and over -- RACE AND HISPANIC OR LATINO ORIGIN -- Hispanic or Latino origin (of any race)</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Total -- Population 16 years and over -- RACE AND HISPANIC OR LATINO ORIGIN -- White alone, not Hispanic or Latino</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Total -- Population 20 to 64 years</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Total -- Population 20 to 64 years -- SEX -- Male</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Total -- Population 20 to 64 years -- SEX -- Female</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Total -- Population 20 to 64 years -- SEX -- Female -- With own children under 6 years</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Total -- POVERTY STATUS IN THE PAST 12 MONTHS -- Below poverty level</t>
-        </is>
-      </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Total -- DISABILITY STATUS -- With any disability</t>
+          <t>Total -- Population 20 to 64 years -- SEX -- Female -- With own children under 18 years</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Total -- EDUCATIONAL ATTAINMENT -- Population 25 to 64 years</t>
+          <t>Total -- Population 20 to 64 years -- SEX -- Female -- With own children under 18 years -- With own children under 6 years only</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Total -- EDUCATIONAL ATTAINMENT -- Population 25 to 64 years -- Less than high school graduate</t>
+          <t>Total -- Population 20 to 64 years -- SEX -- Female -- With own children under 18 years -- With own children under 6 years and 6 to 17  years</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Total -- EDUCATIONAL ATTAINMENT -- Population 25 to 64 years -- High school graduate (includes equivalency)</t>
+          <t>Total -- Population 20 to 64 years -- SEX -- Female -- With own children under 18 years -- With own children 6 to 17 years only</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Total -- EDUCATIONAL ATTAINMENT -- Population 25 to 64 years -- Some college or associate's degree</t>
+          <t>Total -- Population 20 to 64 years -- POVERTY STATUS IN THE PAST 12 MONTHS -- Below poverty level</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Total -- EDUCATIONAL ATTAINMENT -- Population 25 to 64 years -- Bachelor's degree or higher</t>
+          <t>Total -- Population 20 to 64 years -- POVERTY STATUS IN THE PAST 12 MONTHS -- At or above the poverty level</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Total -- PERCENT IMPUTED -- Employment status for population 16 years and over</t>
+          <t>Total -- Population 20 to 64 years -- DISABILITY STATUS -- With any disability</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
@@ -797,152 +797,152 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>In labor force -- Population 16 years and over</t>
+          <t>Labor Force Participation Rate -- Population 16 years and over</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>In labor force -- AGE -- 16 to 19 years</t>
+          <t>Labor Force Participation Rate -- Population 16 years and over -- AGE -- 16 to 19 years</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>In labor force -- AGE -- 20 to 24 years</t>
+          <t>Labor Force Participation Rate -- Population 16 years and over -- AGE -- 20 to 24 years</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>In labor force -- AGE -- 25 to 44 years</t>
+          <t>Labor Force Participation Rate -- Population 16 years and over -- AGE -- 25 to 29 years</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>In labor force -- AGE -- 45 to 54 years</t>
+          <t>Labor Force Participation Rate -- Population 16 years and over -- AGE -- 30 to 34 years</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>In labor force -- AGE -- 55 to 64 years</t>
+          <t>Labor Force Participation Rate -- Population 16 years and over -- AGE -- 35 to 44 years</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>In labor force -- AGE -- 65 to 74 years</t>
+          <t>Labor Force Participation Rate -- Population 16 years and over -- AGE -- 45 to 54 years</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>In labor force -- AGE -- 75 years and over</t>
+          <t>Labor Force Participation Rate -- Population 16 years and over -- AGE -- 55 to 59 years</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>In labor force -- RACE AND HISPANIC OR LATINO ORIGIN -- One race</t>
+          <t>Labor Force Participation Rate -- Population 16 years and over -- AGE -- 60 to 64 years</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>In labor force -- RACE AND HISPANIC OR LATINO ORIGIN -- One race -- White</t>
+          <t>Labor Force Participation Rate -- Population 16 years and over -- AGE -- 65 to 74 years</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>In labor force -- RACE AND HISPANIC OR LATINO ORIGIN -- One race -- Black or African American</t>
+          <t>Labor Force Participation Rate -- Population 16 years and over -- AGE -- 75 years and over</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>In labor force -- RACE AND HISPANIC OR LATINO ORIGIN -- One race -- American Indian and Alaska Native</t>
+          <t>Labor Force Participation Rate -- Population 16 years and over -- RACE AND HISPANIC OR LATINO ORIGIN -- White alone</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>In labor force -- RACE AND HISPANIC OR LATINO ORIGIN -- One race -- Asian</t>
+          <t>Labor Force Participation Rate -- Population 16 years and over -- RACE AND HISPANIC OR LATINO ORIGIN -- Black or African American alone</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>In labor force -- RACE AND HISPANIC OR LATINO ORIGIN -- One race -- Native Hawaiian and Other Pacific Islander</t>
+          <t>Labor Force Participation Rate -- Population 16 years and over -- RACE AND HISPANIC OR LATINO ORIGIN -- American Indian and Alaska Native alone</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>In labor force -- RACE AND HISPANIC OR LATINO ORIGIN -- One race -- Some other race</t>
+          <t>Labor Force Participation Rate -- Population 16 years and over -- RACE AND HISPANIC OR LATINO ORIGIN -- Asian alone</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>In labor force -- RACE AND HISPANIC OR LATINO ORIGIN -- Two or more races</t>
+          <t>Labor Force Participation Rate -- Population 16 years and over -- RACE AND HISPANIC OR LATINO ORIGIN -- Native Hawaiian and Other Pacific Islander alone</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>In labor force -- Hispanic or Latino origin (of any race)</t>
+          <t>Labor Force Participation Rate -- Population 16 years and over -- RACE AND HISPANIC OR LATINO ORIGIN -- Some other race alone</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>In labor force -- White alone, not Hispanic or Latino</t>
+          <t>Labor Force Participation Rate -- Population 16 years and over -- RACE AND HISPANIC OR LATINO ORIGIN -- Two or more races</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
-          <t>In labor force -- Population 20 to 64 years</t>
+          <t>Labor Force Participation Rate -- Population 16 years and over -- RACE AND HISPANIC OR LATINO ORIGIN -- Hispanic or Latino origin (of any race)</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
         <is>
-          <t>In labor force -- Population 20 to 64 years -- SEX -- Male</t>
+          <t>Labor Force Participation Rate -- Population 16 years and over -- RACE AND HISPANIC OR LATINO ORIGIN -- White alone, not Hispanic or Latino</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
         <is>
-          <t>In labor force -- Population 20 to 64 years -- SEX -- Female</t>
+          <t>Labor Force Participation Rate -- Population 20 to 64 years</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
         <is>
-          <t>In labor force -- Population 20 to 64 years -- SEX -- Female -- With own children under 6 years</t>
+          <t>Labor Force Participation Rate -- Population 20 to 64 years -- SEX -- Male</t>
         </is>
       </c>
       <c r="BH1" s="1" t="inlineStr">
         <is>
-          <t>In labor force -- POVERTY STATUS IN THE PAST 12 MONTHS -- Below poverty level</t>
+          <t>Labor Force Participation Rate -- Population 20 to 64 years -- SEX -- Female</t>
         </is>
       </c>
       <c r="BI1" s="1" t="inlineStr">
         <is>
-          <t>In labor force -- DISABILITY STATUS -- With any disability</t>
+          <t>Labor Force Participation Rate -- Population 20 to 64 years -- SEX -- Female -- With own children under 18 years</t>
         </is>
       </c>
       <c r="BJ1" s="1" t="inlineStr">
         <is>
-          <t>In labor force -- EDUCATIONAL ATTAINMENT -- Population 25 to 64 years</t>
+          <t>Labor Force Participation Rate -- Population 20 to 64 years -- SEX -- Female -- With own children under 18 years -- With own children under 6 years only</t>
         </is>
       </c>
       <c r="BK1" s="1" t="inlineStr">
         <is>
-          <t>In labor force -- EDUCATIONAL ATTAINMENT -- Population 25 to 64 years -- Less than high school graduate</t>
+          <t>Labor Force Participation Rate -- Population 20 to 64 years -- SEX -- Female -- With own children under 18 years -- With own children under 6 years and 6 to 17  years</t>
         </is>
       </c>
       <c r="BL1" s="1" t="inlineStr">
         <is>
-          <t>In labor force -- EDUCATIONAL ATTAINMENT -- Population 25 to 64 years -- High school graduate (includes equivalency)</t>
+          <t>Labor Force Participation Rate -- Population 20 to 64 years -- SEX -- Female -- With own children under 18 years -- With own children 6 to 17 years only</t>
         </is>
       </c>
       <c r="BM1" s="1" t="inlineStr">
         <is>
-          <t>In labor force -- EDUCATIONAL ATTAINMENT -- Population 25 to 64 years -- Some college or associate's degree</t>
+          <t>Labor Force Participation Rate -- Population 20 to 64 years -- POVERTY STATUS IN THE PAST 12 MONTHS -- Below poverty level</t>
         </is>
       </c>
       <c r="BN1" s="1" t="inlineStr">
         <is>
-          <t>In labor force -- EDUCATIONAL ATTAINMENT -- Population 25 to 64 years -- Bachelor's degree or higher</t>
+          <t>Labor Force Participation Rate -- Population 20 to 64 years -- POVERTY STATUS IN THE PAST 12 MONTHS -- At or above the poverty level</t>
         </is>
       </c>
       <c r="BO1" s="1" t="inlineStr">
         <is>
-          <t>In labor force -- PERCENT IMPUTED -- Employment status for population 16 years and over</t>
+          <t>Labor Force Participation Rate -- Population 20 to 64 years -- DISABILITY STATUS -- With any disability</t>
         </is>
       </c>
       <c r="BP1" s="1" t="inlineStr">
@@ -972,152 +972,152 @@
       </c>
       <c r="BU1" s="1" t="inlineStr">
         <is>
-          <t>Employed -- Population 16 years and over</t>
+          <t>Employment/Population Ratio -- Population 16 years and over</t>
         </is>
       </c>
       <c r="BV1" s="1" t="inlineStr">
         <is>
-          <t>Employed -- AGE -- 16 to 19 years</t>
+          <t>Employment/Population Ratio -- Population 16 years and over -- AGE -- 16 to 19 years</t>
         </is>
       </c>
       <c r="BW1" s="1" t="inlineStr">
         <is>
-          <t>Employed -- AGE -- 20 to 24 years</t>
+          <t>Employment/Population Ratio -- Population 16 years and over -- AGE -- 20 to 24 years</t>
         </is>
       </c>
       <c r="BX1" s="1" t="inlineStr">
         <is>
-          <t>Employed -- AGE -- 25 to 44 years</t>
+          <t>Employment/Population Ratio -- Population 16 years and over -- AGE -- 25 to 29 years</t>
         </is>
       </c>
       <c r="BY1" s="1" t="inlineStr">
         <is>
-          <t>Employed -- AGE -- 45 to 54 years</t>
+          <t>Employment/Population Ratio -- Population 16 years and over -- AGE -- 30 to 34 years</t>
         </is>
       </c>
       <c r="BZ1" s="1" t="inlineStr">
         <is>
-          <t>Employed -- AGE -- 55 to 64 years</t>
+          <t>Employment/Population Ratio -- Population 16 years and over -- AGE -- 35 to 44 years</t>
         </is>
       </c>
       <c r="CA1" s="1" t="inlineStr">
         <is>
-          <t>Employed -- AGE -- 65 to 74 years</t>
+          <t>Employment/Population Ratio -- Population 16 years and over -- AGE -- 45 to 54 years</t>
         </is>
       </c>
       <c r="CB1" s="1" t="inlineStr">
         <is>
-          <t>Employed -- AGE -- 75 years and over</t>
+          <t>Employment/Population Ratio -- Population 16 years and over -- AGE -- 55 to 59 years</t>
         </is>
       </c>
       <c r="CC1" s="1" t="inlineStr">
         <is>
-          <t>Employed -- RACE AND HISPANIC OR LATINO ORIGIN -- One race</t>
+          <t>Employment/Population Ratio -- Population 16 years and over -- AGE -- 60 to 64 years</t>
         </is>
       </c>
       <c r="CD1" s="1" t="inlineStr">
         <is>
-          <t>Employed -- RACE AND HISPANIC OR LATINO ORIGIN -- One race -- White</t>
+          <t>Employment/Population Ratio -- Population 16 years and over -- AGE -- 65 to 74 years</t>
         </is>
       </c>
       <c r="CE1" s="1" t="inlineStr">
         <is>
-          <t>Employed -- RACE AND HISPANIC OR LATINO ORIGIN -- One race -- Black or African American</t>
+          <t>Employment/Population Ratio -- Population 16 years and over -- AGE -- 75 years and over</t>
         </is>
       </c>
       <c r="CF1" s="1" t="inlineStr">
         <is>
-          <t>Employed -- RACE AND HISPANIC OR LATINO ORIGIN -- One race -- American Indian and Alaska Native</t>
+          <t>Employment/Population Ratio -- Population 16 years and over -- RACE AND HISPANIC OR LATINO ORIGIN -- White alone</t>
         </is>
       </c>
       <c r="CG1" s="1" t="inlineStr">
         <is>
-          <t>Employed -- RACE AND HISPANIC OR LATINO ORIGIN -- One race -- Asian</t>
+          <t>Employment/Population Ratio -- Population 16 years and over -- RACE AND HISPANIC OR LATINO ORIGIN -- Black or African American alone</t>
         </is>
       </c>
       <c r="CH1" s="1" t="inlineStr">
         <is>
-          <t>Employed -- RACE AND HISPANIC OR LATINO ORIGIN -- One race -- Native Hawaiian and Other Pacific Islander</t>
+          <t>Employment/Population Ratio -- Population 16 years and over -- RACE AND HISPANIC OR LATINO ORIGIN -- American Indian and Alaska Native alone</t>
         </is>
       </c>
       <c r="CI1" s="1" t="inlineStr">
         <is>
-          <t>Employed -- RACE AND HISPANIC OR LATINO ORIGIN -- One race -- Some other race</t>
+          <t>Employment/Population Ratio -- Population 16 years and over -- RACE AND HISPANIC OR LATINO ORIGIN -- Asian alone</t>
         </is>
       </c>
       <c r="CJ1" s="1" t="inlineStr">
         <is>
-          <t>Employed -- RACE AND HISPANIC OR LATINO ORIGIN -- Two or more races</t>
+          <t>Employment/Population Ratio -- Population 16 years and over -- RACE AND HISPANIC OR LATINO ORIGIN -- Native Hawaiian and Other Pacific Islander alone</t>
         </is>
       </c>
       <c r="CK1" s="1" t="inlineStr">
         <is>
-          <t>Employed -- Hispanic or Latino origin (of any race)</t>
+          <t>Employment/Population Ratio -- Population 16 years and over -- RACE AND HISPANIC OR LATINO ORIGIN -- Some other race alone</t>
         </is>
       </c>
       <c r="CL1" s="1" t="inlineStr">
         <is>
-          <t>Employed -- White alone, not Hispanic or Latino</t>
+          <t>Employment/Population Ratio -- Population 16 years and over -- RACE AND HISPANIC OR LATINO ORIGIN -- Two or more races</t>
         </is>
       </c>
       <c r="CM1" s="1" t="inlineStr">
         <is>
-          <t>Employed -- Population 20 to 64 years</t>
+          <t>Employment/Population Ratio -- Population 16 years and over -- RACE AND HISPANIC OR LATINO ORIGIN -- Hispanic or Latino origin (of any race)</t>
         </is>
       </c>
       <c r="CN1" s="1" t="inlineStr">
         <is>
-          <t>Employed -- Population 20 to 64 years -- SEX -- Male</t>
+          <t>Employment/Population Ratio -- Population 16 years and over -- RACE AND HISPANIC OR LATINO ORIGIN -- White alone, not Hispanic or Latino</t>
         </is>
       </c>
       <c r="CO1" s="1" t="inlineStr">
         <is>
-          <t>Employed -- Population 20 to 64 years -- SEX -- Female</t>
+          <t>Employment/Population Ratio -- Population 20 to 64 years</t>
         </is>
       </c>
       <c r="CP1" s="1" t="inlineStr">
         <is>
-          <t>Employed -- Population 20 to 64 years -- SEX -- Female -- With own children under 6 years</t>
+          <t>Employment/Population Ratio -- Population 20 to 64 years -- SEX -- Male</t>
         </is>
       </c>
       <c r="CQ1" s="1" t="inlineStr">
         <is>
-          <t>Employed -- POVERTY STATUS IN THE PAST 12 MONTHS -- Below poverty level</t>
+          <t>Employment/Population Ratio -- Population 20 to 64 years -- SEX -- Female</t>
         </is>
       </c>
       <c r="CR1" s="1" t="inlineStr">
         <is>
-          <t>Employed -- DISABILITY STATUS -- With any disability</t>
+          <t>Employment/Population Ratio -- Population 20 to 64 years -- SEX -- Female -- With own children under 18 years</t>
         </is>
       </c>
       <c r="CS1" s="1" t="inlineStr">
         <is>
-          <t>Employed -- EDUCATIONAL ATTAINMENT -- Population 25 to 64 years</t>
+          <t>Employment/Population Ratio -- Population 20 to 64 years -- SEX -- Female -- With own children under 18 years -- With own children under 6 years only</t>
         </is>
       </c>
       <c r="CT1" s="1" t="inlineStr">
         <is>
-          <t>Employed -- EDUCATIONAL ATTAINMENT -- Population 25 to 64 years -- Less than high school graduate</t>
+          <t>Employment/Population Ratio -- Population 20 to 64 years -- SEX -- Female -- With own children under 18 years -- With own children under 6 years and 6 to 17  years</t>
         </is>
       </c>
       <c r="CU1" s="1" t="inlineStr">
         <is>
-          <t>Employed -- EDUCATIONAL ATTAINMENT -- Population 25 to 64 years -- High school graduate (includes equivalency)</t>
+          <t>Employment/Population Ratio -- Population 20 to 64 years -- SEX -- Female -- With own children under 18 years -- With own children 6 to 17 years only</t>
         </is>
       </c>
       <c r="CV1" s="1" t="inlineStr">
         <is>
-          <t>Employed -- EDUCATIONAL ATTAINMENT -- Population 25 to 64 years -- Some college or associate's degree</t>
+          <t>Employment/Population Ratio -- Population 20 to 64 years -- POVERTY STATUS IN THE PAST 12 MONTHS -- Below poverty level</t>
         </is>
       </c>
       <c r="CW1" s="1" t="inlineStr">
         <is>
-          <t>Employed -- EDUCATIONAL ATTAINMENT -- Population 25 to 64 years -- Bachelor's degree or higher</t>
+          <t>Employment/Population Ratio -- Population 20 to 64 years -- POVERTY STATUS IN THE PAST 12 MONTHS -- At or above the poverty level</t>
         </is>
       </c>
       <c r="CX1" s="1" t="inlineStr">
         <is>
-          <t>Employed -- PERCENT IMPUTED -- Employment status for population 16 years and over</t>
+          <t>Employment/Population Ratio -- Population 20 to 64 years -- DISABILITY STATUS -- With any disability</t>
         </is>
       </c>
       <c r="CY1" s="1" t="inlineStr">
@@ -1152,147 +1152,147 @@
       </c>
       <c r="DE1" s="1" t="inlineStr">
         <is>
-          <t>Unemployment rate -- AGE -- 16 to 19 years</t>
+          <t>Unemployment rate -- Population 16 years and over -- AGE -- 16 to 19 years</t>
         </is>
       </c>
       <c r="DF1" s="1" t="inlineStr">
         <is>
-          <t>Unemployment rate -- AGE -- 20 to 24 years</t>
+          <t>Unemployment rate -- Population 16 years and over -- AGE -- 20 to 24 years</t>
         </is>
       </c>
       <c r="DG1" s="1" t="inlineStr">
         <is>
-          <t>Unemployment rate -- AGE -- 25 to 44 years</t>
+          <t>Unemployment rate -- Population 16 years and over -- AGE -- 25 to 29 years</t>
         </is>
       </c>
       <c r="DH1" s="1" t="inlineStr">
         <is>
-          <t>Unemployment rate -- AGE -- 45 to 54 years</t>
+          <t>Unemployment rate -- Population 16 years and over -- AGE -- 30 to 34 years</t>
         </is>
       </c>
       <c r="DI1" s="1" t="inlineStr">
         <is>
-          <t>Unemployment rate -- AGE -- 55 to 64 years</t>
+          <t>Unemployment rate -- Population 16 years and over -- AGE -- 35 to 44 years</t>
         </is>
       </c>
       <c r="DJ1" s="1" t="inlineStr">
         <is>
-          <t>Unemployment rate -- AGE -- 65 to 74 years</t>
+          <t>Unemployment rate -- Population 16 years and over -- AGE -- 45 to 54 years</t>
         </is>
       </c>
       <c r="DK1" s="1" t="inlineStr">
         <is>
-          <t>Unemployment rate -- AGE -- 75 years and over</t>
+          <t>Unemployment rate -- Population 16 years and over -- AGE -- 55 to 59 years</t>
         </is>
       </c>
       <c r="DL1" s="1" t="inlineStr">
         <is>
-          <t>Unemployment rate -- RACE AND HISPANIC OR LATINO ORIGIN -- One race</t>
+          <t>Unemployment rate -- Population 16 years and over -- AGE -- 60 to 64 years</t>
         </is>
       </c>
       <c r="DM1" s="1" t="inlineStr">
         <is>
-          <t>Unemployment rate -- RACE AND HISPANIC OR LATINO ORIGIN -- One race -- White</t>
+          <t>Unemployment rate -- Population 16 years and over -- AGE -- 65 to 74 years</t>
         </is>
       </c>
       <c r="DN1" s="1" t="inlineStr">
         <is>
-          <t>Unemployment rate -- RACE AND HISPANIC OR LATINO ORIGIN -- One race -- Black or African American</t>
+          <t>Unemployment rate -- Population 16 years and over -- AGE -- 75 years and over</t>
         </is>
       </c>
       <c r="DO1" s="1" t="inlineStr">
         <is>
-          <t>Unemployment rate -- RACE AND HISPANIC OR LATINO ORIGIN -- One race -- American Indian and Alaska Native</t>
+          <t>Unemployment rate -- Population 16 years and over -- RACE AND HISPANIC OR LATINO ORIGIN -- White alone</t>
         </is>
       </c>
       <c r="DP1" s="1" t="inlineStr">
         <is>
-          <t>Unemployment rate -- RACE AND HISPANIC OR LATINO ORIGIN -- One race -- Asian</t>
+          <t>Unemployment rate -- Population 16 years and over -- RACE AND HISPANIC OR LATINO ORIGIN -- Black or African American alone</t>
         </is>
       </c>
       <c r="DQ1" s="1" t="inlineStr">
         <is>
-          <t>Unemployment rate -- RACE AND HISPANIC OR LATINO ORIGIN -- One race -- Native Hawaiian and Other Pacific Islander</t>
+          <t>Unemployment rate -- Population 16 years and over -- RACE AND HISPANIC OR LATINO ORIGIN -- American Indian and Alaska Native alone</t>
         </is>
       </c>
       <c r="DR1" s="1" t="inlineStr">
         <is>
-          <t>Unemployment rate -- RACE AND HISPANIC OR LATINO ORIGIN -- One race -- Some other race</t>
+          <t>Unemployment rate -- Population 16 years and over -- RACE AND HISPANIC OR LATINO ORIGIN -- Asian alone</t>
         </is>
       </c>
       <c r="DS1" s="1" t="inlineStr">
         <is>
-          <t>Unemployment rate -- RACE AND HISPANIC OR LATINO ORIGIN -- Two or more races</t>
+          <t>Unemployment rate -- Population 16 years and over -- RACE AND HISPANIC OR LATINO ORIGIN -- Native Hawaiian and Other Pacific Islander alone</t>
         </is>
       </c>
       <c r="DT1" s="1" t="inlineStr">
         <is>
-          <t>Unemployment rate -- Hispanic or Latino origin (of any race)</t>
+          <t>Unemployment rate -- Population 16 years and over -- RACE AND HISPANIC OR LATINO ORIGIN -- Some other race alone</t>
         </is>
       </c>
       <c r="DU1" s="1" t="inlineStr">
         <is>
-          <t>Unemployment rate -- White alone, not Hispanic or Latino</t>
+          <t>Unemployment rate -- Population 16 years and over -- RACE AND HISPANIC OR LATINO ORIGIN -- Two or more races</t>
         </is>
       </c>
       <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>Unemployment rate -- Population 16 years and over -- RACE AND HISPANIC OR LATINO ORIGIN -- Hispanic or Latino origin (of any race)</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>Unemployment rate -- Population 16 years and over -- RACE AND HISPANIC OR LATINO ORIGIN -- White alone, not Hispanic or Latino</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
         <is>
           <t>Unemployment rate -- Population 20 to 64 years</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DY1" s="1" t="inlineStr">
         <is>
           <t>Unemployment rate -- Population 20 to 64 years -- SEX -- Male</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DZ1" s="1" t="inlineStr">
         <is>
           <t>Unemployment rate -- Population 20 to 64 years -- SEX -- Female</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
-        <is>
-          <t>Unemployment rate -- Population 20 to 64 years -- SEX -- Female -- With own children under 6 years</t>
-        </is>
-      </c>
-      <c r="DZ1" s="1" t="inlineStr">
-        <is>
-          <t>Unemployment rate -- POVERTY STATUS IN THE PAST 12 MONTHS -- Below poverty level</t>
-        </is>
-      </c>
       <c r="EA1" s="1" t="inlineStr">
         <is>
-          <t>Unemployment rate -- DISABILITY STATUS -- With any disability</t>
+          <t>Unemployment rate -- Population 20 to 64 years -- SEX -- Female -- With own children under 18 years</t>
         </is>
       </c>
       <c r="EB1" s="1" t="inlineStr">
         <is>
-          <t>Unemployment rate -- EDUCATIONAL ATTAINMENT -- Population 25 to 64 years</t>
+          <t>Unemployment rate -- Population 20 to 64 years -- SEX -- Female -- With own children under 18 years -- With own children under 6 years only</t>
         </is>
       </c>
       <c r="EC1" s="1" t="inlineStr">
         <is>
-          <t>Unemployment rate -- EDUCATIONAL ATTAINMENT -- Population 25 to 64 years -- Less than high school graduate</t>
+          <t>Unemployment rate -- Population 20 to 64 years -- SEX -- Female -- With own children under 18 years -- With own children under 6 years and 6 to 17  years</t>
         </is>
       </c>
       <c r="ED1" s="1" t="inlineStr">
         <is>
-          <t>Unemployment rate -- EDUCATIONAL ATTAINMENT -- Population 25 to 64 years -- High school graduate (includes equivalency)</t>
+          <t>Unemployment rate -- Population 20 to 64 years -- SEX -- Female -- With own children under 18 years -- With own children 6 to 17 years only</t>
         </is>
       </c>
       <c r="EE1" s="1" t="inlineStr">
         <is>
-          <t>Unemployment rate -- EDUCATIONAL ATTAINMENT -- Population 25 to 64 years -- Some college or associate's degree</t>
+          <t>Unemployment rate -- Population 20 to 64 years -- POVERTY STATUS IN THE PAST 12 MONTHS -- Below poverty level</t>
         </is>
       </c>
       <c r="EF1" s="1" t="inlineStr">
         <is>
-          <t>Unemployment rate -- EDUCATIONAL ATTAINMENT -- Population 25 to 64 years -- Bachelor's degree or higher</t>
+          <t>Unemployment rate -- Population 20 to 64 years -- POVERTY STATUS IN THE PAST 12 MONTHS -- At or above the poverty level</t>
         </is>
       </c>
       <c r="EG1" s="1" t="inlineStr">
         <is>
-          <t>Unemployment rate -- PERCENT IMPUTED -- Employment status for population 16 years and over</t>
+          <t>Unemployment rate -- Population 20 to 64 years -- DISABILITY STATUS -- With any disability</t>
         </is>
       </c>
       <c r="EH1" s="1" t="inlineStr">
@@ -24744,14 +24744,14 @@
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>Source: U.S. Census Bureau, American Community Survey 5-Year Estimates, Table S2301 (Employment Status). Variables S2301_C01_001E–S2301_C04_035E (subset varies by year; earlier releases had fewer row indices).</t>
+          <t>Source: U.S. Census Bureau, American Community Survey 5-Year Estimates, Table S2301 (Employment Status). Column labels use the 2024 variable schema. Blank cells indicate a variable did not exist in that year's S2301 release.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>Central New York = Cayuga, Cortland, Madison, Onondaga, and Oswego counties. C01 count variables are summed; C02–C04 rate variables are simple unweighted county averages (see script docstring for weighting limitations).</t>
+          <t>Central New York = Cayuga, Cortland, Madison, Onondaga, and Oswego counties. C01 count variables are summed across counties; C02-C04 rate variables are simple unweighted averages of the five county rates.</t>
         </is>
       </c>
     </row>
